--- a/lab7/analysis/Аналіз_телеметрії_ЛР7.xlsx
+++ b/lab7/analysis/Аналіз_телеметрії_ЛР7.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Значення</t>
   </si>
   <si>
-    <t xml:space="preserve">Формула / пояснення</t>
+    <t xml:space="preserve">Пояснення</t>
   </si>
   <si>
     <t xml:space="preserve">Час армування (початок запису CSV)</t>
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Час торкання землі</t>
   </si>
   <si>
-    <t xml:space="preserve">останній рядок з висотою &gt; 0,3 м</t>
+    <t xml:space="preserve">MAXIFS</t>
   </si>
   <si>
     <t xml:space="preserve">Найбільша висота, м</t>
@@ -135,7 +135,7 @@
     <t xml:space="preserve">DISARMED / DISARMED</t>
   </si>
   <si>
-    <t xml:space="preserve">HEARTBEAT.base_mode: 81 / 89, біт 128 = 0</t>
+    <t xml:space="preserve">HEARTBEAT.base_mode: 81 / 89</t>
   </si>
   <si>
     <t xml:space="preserve">Timestamp</t>
@@ -2032,13 +2032,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="hh:mm:ss"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
     <numFmt numFmtId="167" formatCode="0.0000000"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="hh:mm:ss.000"/>
+    <numFmt numFmtId="168" formatCode="hh:mm:ss.000"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -2171,7 +2170,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2179,7 +2178,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6330,13 +6329,13 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="61082040"/>
-        <c:axId val="48218104"/>
+        <c:axId val="78841619"/>
+        <c:axId val="91653221"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="61082040"/>
+        <c:axId val="78841619"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6412,12 +6411,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48218104"/>
+        <c:crossAx val="91653221"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="48218104"/>
+        <c:axId val="91653221"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6493,7 +6492,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61082040"/>
+        <c:crossAx val="78841619"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -10596,13 +10595,13 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="97415904"/>
-        <c:axId val="89190212"/>
+        <c:axId val="26938430"/>
+        <c:axId val="48519327"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="97415904"/>
+        <c:axId val="26938430"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10678,12 +10677,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89190212"/>
+        <c:crossAx val="48519327"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="89190212"/>
+        <c:axId val="48519327"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10759,7 +10758,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97415904"/>
+        <c:crossAx val="26938430"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -14862,13 +14861,13 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="56486644"/>
-        <c:axId val="15957501"/>
+        <c:axId val="53722608"/>
+        <c:axId val="39947304"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="56486644"/>
+        <c:axId val="53722608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14944,12 +14943,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="15957501"/>
+        <c:crossAx val="39947304"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="15957501"/>
+        <c:axId val="39947304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15025,7 +15024,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56486644"/>
+        <c:crossAx val="53722608"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -15331,9 +15330,9 @@
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="44"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15517,7 +15516,7 @@
         <v>28</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>29</v>
@@ -15593,22 +15592,8 @@
   </sheetPr>
   <dimension ref="A1:Q661"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="0" width="12"/>
-  </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
         <v>38</v>
       </c>
